--- a/branches/master/StructureDefinition-mii-ex-studie-backport-associatedParty.xlsx
+++ b/branches/master/StructureDefinition-mii-ex-studie-backport-associatedParty.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2027.0.0-ballot.rc1</t>
+    <t>2027.0.0-ballot</t>
   </si>
   <si>
     <t>Name</t>
